--- a/Result/profitability/6195.xlsx
+++ b/Result/profitability/6195.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.43625</v>
+        <v>0.43125</v>
       </c>
       <c r="N2" t="n">
-        <v>50.88875</v>
+        <v>50.95125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.32</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4425</v>
+        <v>0.3875</v>
       </c>
       <c r="N3" t="n">
-        <v>45.415</v>
+        <v>45.6275</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.78</v>
       </c>
       <c r="M4" t="n">
-        <v>0.70625</v>
+        <v>0.6475</v>
       </c>
       <c r="N4" t="n">
-        <v>40.2325</v>
+        <v>40.1825</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0.69375</v>
+        <v>0.705</v>
       </c>
       <c r="N5" t="n">
-        <v>33.9475</v>
+        <v>34.02875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6675</v>
+        <v>0.6875</v>
       </c>
       <c r="N6" t="n">
-        <v>28.1225</v>
+        <v>28.24375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.64</v>
       </c>
       <c r="M7" t="n">
-        <v>0.57875</v>
+        <v>0.5975</v>
       </c>
       <c r="N7" t="n">
-        <v>22.41625</v>
+        <v>22.4625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5375</v>
+        <v>0.37875</v>
       </c>
       <c r="N8" t="n">
-        <v>17.37625</v>
+        <v>17.19</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6195</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>571</v>
+      </c>
+      <c r="D75" t="n">
+        <v>248</v>
+      </c>
+      <c r="E75" t="n">
+        <v>323</v>
+      </c>
+      <c r="F75" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="G75" t="n">
+        <v>12</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.05%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>12</v>
+      </c>
+      <c r="K75" t="n">
+        <v>12</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4575</v>
+      </c>
+      <c r="N75" t="n">
+        <v>56.2625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.8466666666666667</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.490000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02567195037904901</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.6428571428571428</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.6499999999999986</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.01162790697674421</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
